--- a/customer_service_forms/019_helpline_status_check_form--customer_service_forms.xlsx
+++ b/customer_service_forms/019_helpline_status_check_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Date Last Contacted</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Date Next Contact</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time Next Contact</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>customer_id_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Customer ID</t>
+          <t>Customer Id 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date_last_contacted</t>
+          <t>date_last_contacted_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date Last Contacted</t>
+          <t>Date Last Contacted 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
